--- a/практическая 1 анализ.xlsx
+++ b/практическая 1 анализ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\handraqw\OpenideProjects\analyze\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04058529-E6C7-40D4-B521-E58EA71312C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE62A0D-0B8E-4288-BD44-E8883DDE360E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{4C7E256E-7AF1-430D-B959-317B8C2BF183}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="5">
   <si>
     <t>x</t>
   </si>
@@ -55,18 +55,6 @@
   </si>
   <si>
     <t>random</t>
-  </si>
-  <si>
-    <t>Сумма</t>
-  </si>
-  <si>
-    <t>Среднее</t>
-  </si>
-  <si>
-    <t>С нарастающим итогом</t>
-  </si>
-  <si>
-    <t>Количество</t>
   </si>
 </sst>
 </file>
@@ -1682,34 +1670,34 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
-                  <c:v>2263690</c:v>
+                  <c:v>2115960</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>15860</c:v>
+                  <c:v>13420</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>45910</c:v>
+                  <c:v>41040</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>88380</c:v>
+                  <c:v>80590</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>161270</c:v>
+                  <c:v>191290</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>337740</c:v>
+                  <c:v>407490</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>690310</c:v>
+                  <c:v>750690</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1558180</c:v>
+                  <c:v>1450350</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>994720</c:v>
+                  <c:v>1208080</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1088870</c:v>
+                  <c:v>1194050</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5782,15 +5770,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>60158</xdr:colOff>
+      <xdr:colOff>33943</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>107281</xdr:rowOff>
+      <xdr:rowOff>19896</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>21</xdr:col>
-      <xdr:colOff>350921</xdr:colOff>
+      <xdr:colOff>324706</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>183481</xdr:rowOff>
+      <xdr:rowOff>96096</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -7601,38 +7589,38 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>2077200</v>
+        <v>2030700</v>
       </c>
       <c r="C3">
-        <v>2541400</v>
+        <v>2221000</v>
       </c>
       <c r="D3" s="1">
-        <v>2873600</v>
+        <v>2283200</v>
       </c>
       <c r="E3">
-        <v>2015600</v>
+        <v>2264800</v>
       </c>
       <c r="F3">
-        <v>2144400</v>
+        <v>2122200</v>
       </c>
       <c r="G3">
-        <v>2069600</v>
+        <v>2517300</v>
       </c>
       <c r="H3">
-        <v>2327100</v>
+        <v>1504000</v>
       </c>
       <c r="I3">
-        <v>2055200</v>
+        <v>1851600</v>
       </c>
       <c r="J3">
-        <v>2706000</v>
+        <v>2601400</v>
       </c>
       <c r="K3">
-        <v>1826800</v>
+        <v>1763400</v>
       </c>
       <c r="L3" s="2">
-        <f t="shared" ref="L3:L12" si="0">AVERAGE(B3:K3)</f>
-        <v>2263690</v>
+        <f>AVERAGE(B3:K3)</f>
+        <v>2115960</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
@@ -7640,38 +7628,38 @@
         <v>100</v>
       </c>
       <c r="B4">
+        <v>12400</v>
+      </c>
+      <c r="C4">
+        <v>11900</v>
+      </c>
+      <c r="D4">
+        <v>11200</v>
+      </c>
+      <c r="E4">
+        <v>23200</v>
+      </c>
+      <c r="F4">
         <v>11000</v>
       </c>
-      <c r="C4">
-        <v>27900</v>
-      </c>
-      <c r="D4">
-        <v>11800</v>
-      </c>
-      <c r="E4">
-        <v>25000</v>
-      </c>
-      <c r="F4">
-        <v>11800</v>
-      </c>
       <c r="G4">
+        <v>17300</v>
+      </c>
+      <c r="H4">
+        <v>13100</v>
+      </c>
+      <c r="I4">
+        <v>10200</v>
+      </c>
+      <c r="J4">
+        <v>12300</v>
+      </c>
+      <c r="K4">
         <v>11600</v>
       </c>
-      <c r="H4">
-        <v>10600</v>
-      </c>
-      <c r="I4">
-        <v>12500</v>
-      </c>
-      <c r="J4">
-        <v>11300</v>
-      </c>
-      <c r="K4">
-        <v>25100</v>
-      </c>
       <c r="L4" s="2">
-        <f t="shared" si="0"/>
-        <v>15860</v>
+        <f t="shared" ref="L4:L12" si="0">AVERAGE(B4:K4)</f>
+        <v>13420</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
@@ -7679,42 +7667,42 @@
         <v>1000</v>
       </c>
       <c r="B5">
-        <v>37900</v>
+        <v>39000</v>
       </c>
       <c r="C5">
-        <v>36700</v>
+        <v>41000</v>
       </c>
       <c r="D5">
-        <v>41300</v>
+        <v>40500</v>
       </c>
       <c r="E5">
-        <v>121700</v>
+        <v>37100</v>
       </c>
       <c r="F5">
         <v>29800</v>
       </c>
       <c r="G5">
-        <v>37700</v>
+        <v>39800</v>
       </c>
       <c r="H5">
-        <v>36200</v>
+        <v>40200</v>
       </c>
       <c r="I5">
-        <v>39100</v>
+        <v>64500</v>
       </c>
       <c r="J5">
-        <v>39900</v>
+        <v>39300</v>
       </c>
       <c r="K5">
-        <v>38800</v>
+        <v>39200</v>
       </c>
       <c r="L5" s="2">
         <f t="shared" si="0"/>
-        <v>45910</v>
+        <v>41040</v>
       </c>
       <c r="M5">
         <f t="shared" ref="M5:M12" si="1">L5/L4</f>
-        <v>2.8947036569987388</v>
+        <v>3.0581222056631892</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
@@ -7722,42 +7710,42 @@
         <v>2000</v>
       </c>
       <c r="B6">
-        <v>91200</v>
+        <v>74300</v>
       </c>
       <c r="C6">
-        <v>85200</v>
+        <v>58200</v>
       </c>
       <c r="D6">
-        <v>73900</v>
+        <v>80000</v>
       </c>
       <c r="E6">
-        <v>96800</v>
+        <v>147100</v>
       </c>
       <c r="F6">
-        <v>94500</v>
+        <v>57300</v>
       </c>
       <c r="G6">
-        <v>159700</v>
+        <v>78400</v>
       </c>
       <c r="H6">
-        <v>70300</v>
+        <v>75600</v>
       </c>
       <c r="I6">
-        <v>74900</v>
+        <v>76600</v>
       </c>
       <c r="J6">
-        <v>79500</v>
+        <v>92600</v>
       </c>
       <c r="K6">
-        <v>57800</v>
+        <v>65800</v>
       </c>
       <c r="L6" s="2">
         <f t="shared" si="0"/>
-        <v>88380</v>
+        <v>80590</v>
       </c>
       <c r="M6">
         <f t="shared" si="1"/>
-        <v>1.9250707906774123</v>
+        <v>1.9636939571150098</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
@@ -7765,42 +7753,42 @@
         <v>4000</v>
       </c>
       <c r="B7">
-        <v>137400</v>
+        <v>144100</v>
       </c>
       <c r="C7">
-        <v>138100</v>
+        <v>174600</v>
       </c>
       <c r="D7">
-        <v>236200</v>
+        <v>137200</v>
       </c>
       <c r="E7">
-        <v>242700</v>
+        <v>138600</v>
       </c>
       <c r="F7">
-        <v>111100</v>
+        <v>136200</v>
       </c>
       <c r="G7">
-        <v>135600</v>
+        <v>150300</v>
       </c>
       <c r="H7">
-        <v>168900</v>
+        <v>375500</v>
       </c>
       <c r="I7">
-        <v>192500</v>
+        <v>132500</v>
       </c>
       <c r="J7">
-        <v>138100</v>
+        <v>368100</v>
       </c>
       <c r="K7">
-        <v>112100</v>
+        <v>155800</v>
       </c>
       <c r="L7" s="2">
         <f t="shared" si="0"/>
-        <v>161270</v>
+        <v>191290</v>
       </c>
       <c r="M7">
         <f t="shared" si="1"/>
-        <v>1.824734102738176</v>
+        <v>2.373619555776151</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
@@ -7808,42 +7796,42 @@
         <v>8000</v>
       </c>
       <c r="B8">
-        <v>370000</v>
+        <v>524700</v>
       </c>
       <c r="C8">
-        <v>379400</v>
+        <v>328200</v>
       </c>
       <c r="D8">
-        <v>289200</v>
+        <v>283200</v>
       </c>
       <c r="E8">
-        <v>312600</v>
+        <v>358200</v>
       </c>
       <c r="F8">
-        <v>226600</v>
+        <v>292500</v>
       </c>
       <c r="G8">
-        <v>673800</v>
+        <v>635200</v>
       </c>
       <c r="H8">
-        <v>289700</v>
+        <v>601800</v>
       </c>
       <c r="I8">
-        <v>310300</v>
+        <v>411900</v>
       </c>
       <c r="J8">
+        <v>341600</v>
+      </c>
+      <c r="K8">
         <v>297600</v>
-      </c>
-      <c r="K8">
-        <v>228200</v>
       </c>
       <c r="L8" s="2">
         <f t="shared" si="0"/>
-        <v>337740</v>
+        <v>407490</v>
       </c>
       <c r="M8">
         <f t="shared" si="1"/>
-        <v>2.0942518757363429</v>
+        <v>2.13022113022113</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
@@ -7851,42 +7839,42 @@
         <v>16000</v>
       </c>
       <c r="B9" s="1">
-        <v>613900</v>
+        <v>628200</v>
       </c>
       <c r="C9">
-        <v>1448500</v>
+        <v>566100</v>
       </c>
       <c r="D9">
-        <v>573200</v>
+        <v>618700</v>
       </c>
       <c r="E9">
-        <v>638000</v>
+        <v>556000</v>
       </c>
       <c r="F9">
-        <v>565000</v>
+        <v>852300</v>
       </c>
       <c r="G9">
-        <v>692200</v>
+        <v>1338600</v>
       </c>
       <c r="H9">
-        <v>469800</v>
+        <v>1342900</v>
       </c>
       <c r="I9">
-        <v>657900</v>
+        <v>487800</v>
       </c>
       <c r="J9">
-        <v>637000</v>
+        <v>574600</v>
       </c>
       <c r="K9">
-        <v>607600</v>
+        <v>541700</v>
       </c>
       <c r="L9" s="2">
         <f t="shared" si="0"/>
-        <v>690310</v>
+        <v>750690</v>
       </c>
       <c r="M9">
         <f t="shared" si="1"/>
-        <v>2.0439095161958902</v>
+        <v>1.842229257159685</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
@@ -7894,42 +7882,42 @@
         <v>32000</v>
       </c>
       <c r="B10">
-        <v>1253200</v>
+        <v>1155300</v>
       </c>
       <c r="C10">
-        <v>1210700</v>
+        <v>1693000</v>
       </c>
       <c r="D10">
-        <v>2034800</v>
+        <v>1143900</v>
       </c>
       <c r="E10">
-        <v>1280200</v>
+        <v>1237800</v>
       </c>
       <c r="F10">
-        <v>1566800</v>
+        <v>2951200</v>
       </c>
       <c r="G10">
-        <v>1359100</v>
+        <v>1121300</v>
       </c>
       <c r="H10">
-        <v>3155900</v>
+        <v>1293500</v>
       </c>
       <c r="I10">
-        <v>1334400</v>
+        <v>1247600</v>
       </c>
       <c r="J10">
-        <v>1303700</v>
+        <v>1229400</v>
       </c>
       <c r="K10">
-        <v>1083000</v>
+        <v>1430500</v>
       </c>
       <c r="L10" s="2">
         <f t="shared" si="0"/>
-        <v>1558180</v>
+        <v>1450350</v>
       </c>
       <c r="M10">
         <f t="shared" si="1"/>
-        <v>2.2572177717257462</v>
+        <v>1.9320225392638772</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
@@ -7937,42 +7925,42 @@
         <v>64000</v>
       </c>
       <c r="B11">
-        <v>2495400</v>
+        <v>1365900</v>
       </c>
       <c r="C11">
-        <v>361600</v>
+        <v>1943200</v>
       </c>
       <c r="D11">
-        <v>483200</v>
+        <v>1172300</v>
       </c>
       <c r="E11">
-        <v>356900</v>
+        <v>1567800</v>
       </c>
       <c r="F11">
-        <v>500200</v>
+        <v>1869800</v>
       </c>
       <c r="G11">
-        <v>943800</v>
+        <v>1793900</v>
       </c>
       <c r="H11">
-        <v>1012800</v>
+        <v>594500</v>
       </c>
       <c r="I11">
-        <v>1665600</v>
+        <v>502900</v>
       </c>
       <c r="J11">
-        <v>1770300</v>
+        <v>617100</v>
       </c>
       <c r="K11">
-        <v>357400</v>
+        <v>653400</v>
       </c>
       <c r="L11" s="2">
         <f t="shared" si="0"/>
-        <v>994720</v>
+        <v>1208080</v>
       </c>
       <c r="M11">
         <f t="shared" si="1"/>
-        <v>0.63838580908495812</v>
+        <v>0.83295756196780091</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -7980,42 +7968,42 @@
         <v>128000</v>
       </c>
       <c r="B12">
-        <v>674300</v>
+        <v>1038400</v>
       </c>
       <c r="C12">
-        <v>1005600</v>
+        <v>765600</v>
       </c>
       <c r="D12">
-        <v>947500</v>
+        <v>1444100</v>
       </c>
       <c r="E12">
-        <v>1739600</v>
+        <v>1098300</v>
       </c>
       <c r="F12">
-        <v>971000</v>
+        <v>1273400</v>
       </c>
       <c r="G12">
-        <v>1384000</v>
+        <v>1289300</v>
       </c>
       <c r="H12">
-        <v>1014200</v>
+        <v>1561100</v>
       </c>
       <c r="I12">
-        <v>841200</v>
+        <v>1222300</v>
       </c>
       <c r="J12">
-        <v>1091200</v>
+        <v>1305400</v>
       </c>
       <c r="K12">
-        <v>1220100</v>
+        <v>942600</v>
       </c>
       <c r="L12" s="2">
         <f t="shared" si="0"/>
-        <v>1088870</v>
+        <v>1194050</v>
       </c>
       <c r="M12">
         <f t="shared" si="1"/>
-        <v>1.0946497506836095</v>
+        <v>0.9883865306933316</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -8600,7 +8588,7 @@
         <v>1506500</v>
       </c>
       <c r="L33" s="2">
-        <f t="shared" ref="L33:L43" si="4">AVERAGE(B33:K33)</f>
+        <f t="shared" ref="L33:L41" si="4">AVERAGE(B33:K33)</f>
         <v>2044350</v>
       </c>
     </row>
